--- a/data/trending_integrated_20260917_11.xlsx
+++ b/data/trending_integrated_20260917_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급격한 등락률을 보이며 300원 돌파 및 지분 매수 공시 가능성을 언급, 개미 투자자들의 매수 심리를 이용한 가격 조작 가능성 제기.</t>
+          <t>저가 매수 및 급등 기대감 혼재. 지분 매수 공시 부재 및 회사의 문제점 지적. 300원 돌파 및 100원대 진입 예상.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['등락률', '지분 매수', '가격 조작']</t>
+          <t>['저가 매수', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1669</v>
+        <v>1690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.47%</t>
+          <t>'+20.97%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
         <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>3.52</v>
@@ -702,7 +702,7 @@
         <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>37910128578</v>
+        <v>39503181400</v>
       </c>
       <c r="P3" t="n">
         <v>5140</v>
@@ -711,7 +711,7 @@
         <v>870</v>
       </c>
       <c r="R3" t="n">
-        <v>222000</v>
+        <v>72000</v>
       </c>
       <c r="S3" t="n">
         <v>-7000</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22100</v>
+        <v>4585</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.07%</t>
+          <t>'+19.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>765</v>
       </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>0.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18560</v>
+        <v>3840</v>
       </c>
       <c r="K4" t="n">
-        <v>19260</v>
+        <v>4170</v>
       </c>
       <c r="L4" t="n">
-        <v>22950</v>
+        <v>4585</v>
       </c>
       <c r="M4" t="n">
-        <v>18920</v>
+        <v>3990</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>234672273620</v>
+        <v>151956114093</v>
       </c>
       <c r="P4" t="n">
-        <v>59600</v>
+        <v>6900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1030</v>
+        <v>1738</v>
       </c>
       <c r="R4" t="n">
-        <v>-45000</v>
+        <v>-159000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 CPO 생산 장비 수주 및 광통신 섹터 대장주 부각. 루멘텀 급등.</t>
+          <t>카카오 또는 소프트뱅크 인수설 기대감. 10배 상승 가능성 및 텐버거 언급. 흑자 기업 PBR 저평가 주장.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['CPO', '광통신', '수주']</t>
+          <t>['인수설', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4360</v>
+        <v>21800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.54%</t>
+          <t>'+17.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>654</v>
+        <v>179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,60 +871,60 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K5" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L5" t="n">
-        <v>4500</v>
+        <v>22950</v>
       </c>
       <c r="M5" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>142922748650</v>
+        <v>239311509995</v>
       </c>
       <c r="P5" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q5" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R5" t="n">
-        <v>101000</v>
+        <v>-78000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 관련 루머 확산. 텐버거 기대감 높은 상황.</t>
+          <t>자회사 CPO 생산 장비 수주 및 광통신 섹터 대장주 부각. 루멘텀 급등.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['CPO', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3785</v>
+        <v>3860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+10.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>66405899329</v>
+        <v>71357429258</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -987,7 +987,7 @@
         <v>1913</v>
       </c>
       <c r="R6" t="n">
-        <v>-1017000</v>
+        <v>-519000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10660</v>
+        <v>21600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.92%</t>
+          <t>'+6.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>28.36</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9970</v>
+        <v>20200</v>
       </c>
       <c r="K7" t="n">
-        <v>10280</v>
+        <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>11750</v>
+        <v>21750</v>
       </c>
       <c r="M7" t="n">
-        <v>10250</v>
+        <v>20450</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>158590756890</v>
+        <v>46691111675</v>
       </c>
       <c r="P7" t="n">
-        <v>15960</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3500</v>
+        <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>350000</v>
+        <v>902000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>낙태약 도입 및 탈모 치료 관련주로 거론되나, 주가를 올린 주체는 이탈 중이며 개인 매도 물량이 나오고 있다는 분석.</t>
+          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 유지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '매출']</t>
+          <t>['나스닥', '금리인상', '투자의견']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21550</v>
+        <v>10570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.68%</t>
+          <t>'+6.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.15</v>
+        <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="H8" t="n">
-        <v>28.36</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20200</v>
+        <v>9970</v>
       </c>
       <c r="K8" t="n">
-        <v>20450</v>
+        <v>10280</v>
       </c>
       <c r="L8" t="n">
-        <v>21750</v>
+        <v>11750</v>
       </c>
       <c r="M8" t="n">
-        <v>20450</v>
+        <v>10250</v>
       </c>
       <c r="N8" t="n">
-        <v>28.51</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>43935357800</v>
+        <v>160513984845</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>15960</v>
       </c>
       <c r="Q8" t="n">
-        <v>18440</v>
+        <v>3500</v>
       </c>
       <c r="R8" t="n">
-        <v>400000</v>
+        <v>21000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 유지.</t>
+          <t>낙태약 및 탈모 치료제 관련 수혜 기대. 외인 매도 및 개인 물량 이탈 관측. 2만원 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['나스닥', '금리인상', '투자의견']</t>
+          <t>['낙태약', '탈모 치료제']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13470</v>
+        <v>13380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.26%</t>
+          <t>'+3.56%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>42579206285</v>
+        <v>44482889950</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1263,7 +1263,7 @@
         <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-80000</v>
+        <v>-110000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>74084596500</v>
+        <v>76920164800</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1391,184 +1391,184 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16280</v>
+        <v>18700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.12%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>919</v>
+        <v>266</v>
       </c>
       <c r="H11" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K11" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L11" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M11" t="n">
-        <v>15560</v>
+        <v>18580</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>272895215545</v>
+        <v>35036275150</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-173000</v>
+        <v>-175000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 상승에 따른 수혜 기대감과 세계적인 통신 장비 부족을 호재로 분석, 2만 원 돌파 전망.</t>
+          <t>6천억 수주 발표 및 대차해지 운동 언급. 정부의 웨스팅하우스 지분 인수 타진 소식.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '통신 장비', '호재']</t>
+          <t>['수주', '대차해지', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18690</v>
+        <v>16160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="G12" t="n">
-        <v>250</v>
+        <v>944</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M12" t="n">
-        <v>18580</v>
+        <v>15560</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>33861365675</v>
+        <v>279341810365</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-143000</v>
+        <v>-508000</v>
       </c>
       <c r="S12" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6천억 수주 발표 및 대차해지 운동 언급. 정부의 웨스팅하우스 지분 인수 타진 소식.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대. 통신 장비 부족 이슈. 2만 원 목표 주가 및 매물대 소화 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '웨스팅하우스']</t>
+          <t>['광통신', '통신 장비']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252500</v>
+        <v>252250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.39%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G13" t="n">
-        <v>2150</v>
+        <v>2126</v>
       </c>
       <c r="H13" t="n">
         <v>46.52</v>
@@ -1622,7 +1622,7 @@
         <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>1067150932750</v>
+        <v>1108134080750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1631,23 +1631,23 @@
         <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-149000</v>
+        <v>-199000</v>
       </c>
       <c r="S13" t="n">
-        <v>-85000</v>
+        <v>-55000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대통령 관련 정치적 논쟁과 증시 악재 언급이 주를 이루며, 반도체 섹터의 미국 증시 움직임을 주시하고 있음.</t>
+          <t>정치 관련 논쟁 심화. 증시 악재 언급. 특정 정치인 지지 및 비판. 반도체 업황 낙관론 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['증시 악재', '반도체', '정치']</t>
+          <t>['정치', '증시']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,123 +1667,123 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3505</v>
+        <v>1747000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>460</v>
       </c>
       <c r="G14" t="n">
-        <v>242</v>
+        <v>1465</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>50.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3520</v>
+        <v>1759000</v>
       </c>
       <c r="K14" t="n">
-        <v>3730</v>
+        <v>1770000</v>
       </c>
       <c r="L14" t="n">
-        <v>3750</v>
+        <v>1785000</v>
       </c>
       <c r="M14" t="n">
-        <v>3460</v>
+        <v>1735000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.11</v>
+        <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4662740271</v>
+        <v>2010103380000</v>
       </c>
       <c r="P14" t="n">
-        <v>16110</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>2300</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-276000</v>
+        <v>-161000</v>
       </c>
       <c r="S14" t="n">
-        <v>-9000</v>
+        <v>-55000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>차익 실현 매물 출회 및 급락 추세. 소식 부재와 무자비한 주가 움직임.</t>
+          <t>반도체 업황 회복 기대감. 미국 금리 인상 우려 속 상승 전환 가능성 언급. 물량 매집 관측.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '주가흐름']</t>
+          <t>['반도체', '금리 인상']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1749000</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.57%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
-        <v>459</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>1474</v>
+        <v>209</v>
       </c>
       <c r="H15" t="n">
-        <v>50.2</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1759000</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>1770000</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>1785000</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>1735000</v>
+        <v>8360</v>
       </c>
       <c r="N15" t="n">
-        <v>50.2</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1935813484500</v>
+        <v>8319294955</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-172000</v>
+        <v>-263000</v>
       </c>
       <c r="S15" t="n">
-        <v>-29000</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주요 악재 소멸 후 상승세를 기대하며, ADR 괴리율과 JP모간의 움직임을 관망하고 있음.</t>
+          <t>중국 디스플레이 업체와의 경쟁 심화. 부채 부담 및 경영 능력 비판. 주가 하락 지속 및 반등 가능성 희박.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['ADR', '상승각', '괴리율']</t>
+          <t>['디스플레이', '경쟁력']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8420</v>
+        <v>13780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="H16" t="n">
-        <v>26.54</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8470</v>
+        <v>13970</v>
       </c>
       <c r="K16" t="n">
-        <v>8470</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>8510</v>
+        <v>13970</v>
       </c>
       <c r="M16" t="n">
-        <v>8360</v>
+        <v>13410</v>
       </c>
       <c r="N16" t="n">
-        <v>26.66</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>8139615925</v>
+        <v>11922807020</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-169000</v>
+        <v>132000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업에 대한 경쟁력 약화 및 높은 부채 비율로 인한 부정적 전망. 경영 능력 의문 제기.</t>
+          <t>겨울철 유가 상승 기대감과 조정 가능성 혼재. 외인 대량 매수 관측 및 패턴 분석. 두바이유 가격 변동성에 주목.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['중국', '영업이익', '부채']</t>
+          <t>['유가', '겨울']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13270</v>
+        <v>3465</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.92%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.36</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="H17" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13530</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>14280</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>13130</v>
+        <v>3460</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>74273302990</v>
+        <v>4742677877</v>
       </c>
       <c r="P17" t="n">
-        <v>25700</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>2000</v>
+        <v>-279000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>차익 실현 매물 출회 및 급락 추세. 소식 부재와 무자비한 주가 움직임.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['차익실현', '급락', '주가흐름']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13700</v>
+        <v>13120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.93%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>270</v>
+        <v>71</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13970</v>
+        <v>13530</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>14280</v>
       </c>
       <c r="L18" t="n">
-        <v>13970</v>
+        <v>14800</v>
       </c>
       <c r="M18" t="n">
-        <v>13410</v>
+        <v>13110</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>11681498180</v>
+        <v>75667379940</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>25700</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>4600</v>
       </c>
       <c r="R18" t="n">
-        <v>116000</v>
+        <v>-64000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유가 하락 추세에 따라 하락세를 예상하며, VI 발동 가능성과 함께 유가 변동성에 따른 주가 움직임을 관망.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유가 하락', 'VI', '변동성']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10220</v>
+        <v>10110</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" t="n">
         <v>34</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>49356010645</v>
+        <v>50638569185</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2183,10 +2183,10 @@
         <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-39000</v>
+        <v>-60000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4160</v>
+        <v>4115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.67%</t>
+          <t>'-6.69%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2260,13 +2260,13 @@
         <v>4420</v>
       </c>
       <c r="M20" t="n">
-        <v>4120</v>
+        <v>4115</v>
       </c>
       <c r="N20" t="n">
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>34842148190</v>
+        <v>36222569279</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2275,7 +2275,7 @@
         <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>23000</v>
+        <v>-161000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260917_11.xlsx
+++ b/data/trending_integrated_20260917_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>저가 매수 및 급등 기대감 혼재. 지분 매수 공시 부재 및 회사의 문제점 지적. 300원 돌파 및 100원대 진입 예상.</t>
+          <t>300원대 돌파 및 상승 기대감 존재. 회사 문제 없음에도 불구하고 주가 하락 우려. 마이크로LED, AI 데이터센터 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['저가 매수', '급등']</t>
+          <t>['마이크로LED', 'AI데이터센터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1690</v>
+        <v>4670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.97%</t>
+          <t>'+21.61%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>325</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>844</v>
       </c>
       <c r="H3" t="n">
-        <v>3.52</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1397</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>1395</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>1800</v>
+        <v>4670</v>
       </c>
       <c r="M3" t="n">
-        <v>1369</v>
+        <v>3990</v>
       </c>
       <c r="N3" t="n">
-        <v>3.57</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>39503181400</v>
+        <v>173650549873</v>
       </c>
       <c r="P3" t="n">
-        <v>5140</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>870</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>72000</v>
+        <v>-159000</v>
       </c>
       <c r="S3" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>카카오 및 소프트뱅크 인수 가능성에 대한 높은 기대감 형성. 텐버거 및 10배 상승 전망. 거래량 폭발 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['카카오', '소프트뱅크', '인수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4585</v>
+        <v>1661</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.40%</t>
+          <t>'+18.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>297</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>765</v>
+        <v>99</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>3.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>1397</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>1395</v>
       </c>
       <c r="L4" t="n">
-        <v>4585</v>
+        <v>1800</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>1369</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>151956114093</v>
+        <v>40208797445</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>5140</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>-159000</v>
+        <v>72000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 또는 소프트뱅크 인수설 기대감. 10배 상승 가능성 및 텐버거 언급. 흑자 기업 PBR 저평가 주장.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수설', '텐버거']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21800</v>
+        <v>21550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.46%</t>
+          <t>'+16.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>239311509995</v>
+        <v>243513941620</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3860</v>
+        <v>3870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.29%</t>
+          <t>'+10.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>71357429258</v>
+        <v>73909897005</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>프로그램 매도세와 함께 급등락이 반복되는 양상이며, 스페이스 이슈와 연관성이 있으나 현재 주가 흐름은 부정적.</t>
+          <t>우주 섹터 관련 기대감 있으나, 주가 하락 및 매집봉 형성 가능성 언급. 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['프로그램 매도', '스페이스 이슈', '급등락']</t>
+          <t>['우주섹터', '매집봉']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>46691111675</v>
+        <v>47959385250</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 유지.</t>
+          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 투자 의견 유지. 단기 스퀴즈 및 자사주 소각 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['나스닥', '금리인상', '투자의견']</t>
+          <t>['나스닥', '금리인상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10570</v>
+        <v>10470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.02%</t>
+          <t>'+5.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>160513984845</v>
+        <v>164295493130</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 수혜 기대. 외인 매도 및 개인 물량 이탈 관측. 2만원 목표 주가 언급.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감 존재. 그러나 매도 물량 출회 및 개인 투자자 손실 발생 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모 치료제']</t>
+          <t>['낙태약', '탈모치료']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13380</v>
+        <v>13490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.56%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>44482889950</v>
+        <v>46089312255</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85800</v>
+        <v>85900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" t="n">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>76920164800</v>
+        <v>78596810050</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18700</v>
+        <v>18660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="H11" t="n">
         <v>10.85</v>
@@ -1438,7 +1438,7 @@
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>35036275150</v>
+        <v>35922481645</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16160</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>192</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>437</v>
       </c>
       <c r="G12" t="n">
-        <v>944</v>
+        <v>2090</v>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K12" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L12" t="n">
-        <v>16750</v>
+        <v>259000</v>
       </c>
       <c r="M12" t="n">
-        <v>15560</v>
+        <v>252000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>279341810365</v>
+        <v>1165363148500</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-508000</v>
+        <v>-199000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대. 통신 장비 부족 이슈. 2만 원 목표 주가 및 매물대 소화 언급.</t>
+          <t>게시글 대부분이 정치 관련 내용으로, 주가 분석과 관련 없는 내용이 주를 이룸.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '통신 장비']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252250</v>
+        <v>16000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.49%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>197</v>
       </c>
       <c r="F13" t="n">
-        <v>436</v>
+        <v>109</v>
       </c>
       <c r="G13" t="n">
-        <v>2126</v>
+        <v>960</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>16100</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>16200</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>16750</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>15560</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1108134080750</v>
+        <v>290610491960</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-199000</v>
+        <v>-508000</v>
       </c>
       <c r="S13" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치 관련 논쟁 심화. 증시 악재 언급. 특정 정치인 지지 및 비판. 반도체 업황 낙관론 혼재.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대. 통신 장비 부족 이슈. 2만 원 목표 주가 및 매물대 소화 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '증시']</t>
+          <t>['광통신', '통신 장비']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1747000</v>
+        <v>8410</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>460</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>1465</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
-        <v>50.2</v>
+        <v>26.54</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1759000</v>
+        <v>8470</v>
       </c>
       <c r="K14" t="n">
-        <v>1770000</v>
+        <v>8470</v>
       </c>
       <c r="L14" t="n">
-        <v>1785000</v>
+        <v>8510</v>
       </c>
       <c r="M14" t="n">
-        <v>1735000</v>
+        <v>8360</v>
       </c>
       <c r="N14" t="n">
-        <v>50.2</v>
+        <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>2010103380000</v>
+        <v>8513434520</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-161000</v>
+        <v>-263000</v>
       </c>
       <c r="S14" t="n">
-        <v>-55000</v>
+        <v>4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 업황 회복 기대감. 미국 금리 인상 우려 속 상승 전환 가능성 언급. 물량 매집 관측.</t>
+          <t>중국 디스플레이 업체와의 경쟁 심화. 부채 부담 및 경영 능력 비판. 주가 하락 지속 및 반등 가능성 희박.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '금리 인상']</t>
+          <t>['디스플레이', '경쟁력']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8400</v>
+        <v>1744000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>465</v>
       </c>
       <c r="G15" t="n">
-        <v>209</v>
+        <v>1470</v>
       </c>
       <c r="H15" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K15" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L15" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M15" t="n">
-        <v>8360</v>
+        <v>1735000</v>
       </c>
       <c r="N15" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O15" t="n">
-        <v>8319294955</v>
+        <v>2078334636500</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R15" t="n">
-        <v>-263000</v>
+        <v>-161000</v>
       </c>
       <c r="S15" t="n">
-        <v>4000</v>
+        <v>-55000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>중국 디스플레이 업체와의 경쟁 심화. 부채 부담 및 경영 능력 비판. 주가 하락 지속 및 반등 가능성 희박.</t>
+          <t>대만 증시 상승 및 악재 소멸 후 상승 기대감 형성. 개인 투자자의 매도 유도 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['디스플레이', '경쟁력']</t>
+          <t>['대만', '악재소멸']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>11922807020</v>
+        <v>12150810760</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>겨울철 유가 상승 기대감과 조정 가능성 혼재. 외인 대량 매수 관측 및 패턴 분석. 두바이유 가격 변동성에 주목.</t>
+          <t>유가 상승 및 겨울 도래로 인한 긍정적 전망과 하락 가능성 공존. 유가 조정 시 등락 반복 패턴 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3465</v>
+        <v>3470</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
         <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H17" t="n">
         <v>2.26</v>
@@ -1984,13 +1984,13 @@
         <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>3460</v>
+        <v>3445</v>
       </c>
       <c r="N17" t="n">
         <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>4742677877</v>
+        <v>4920005731</v>
       </c>
       <c r="P17" t="n">
         <v>16110</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>차익 실현 매물 출회 및 급락 추세. 소식 부재와 무자비한 주가 움직임.</t>
+          <t>주가 급락 및 폭락에 대한 우려 제기. 상승 가능성 희박하며 상장 폐지 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '주가흐름']</t>
+          <t>['급락', '상장폐지']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>75667379940</v>
+        <v>76147477060</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10110</v>
+        <v>10080</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2168,13 +2168,13 @@
         <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>10080</v>
+        <v>10060</v>
       </c>
       <c r="N19" t="n">
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>50638569185</v>
+        <v>52118859105</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4115</v>
+        <v>4100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.69%</t>
+          <t>'-7.03%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2260,13 +2260,13 @@
         <v>4420</v>
       </c>
       <c r="M20" t="n">
-        <v>4115</v>
+        <v>4100</v>
       </c>
       <c r="N20" t="n">
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>36222569279</v>
+        <v>37620293434</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_11.xlsx
+++ b/data/trending_integrated_20260917_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+48.21%</t>
+          <t>'+28.57%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -610,7 +610,7 @@
         <v>3.71</v>
       </c>
       <c r="O2" t="n">
-        <v>333619574</v>
+        <v>389595614</v>
       </c>
       <c r="P2" t="n">
         <v>901</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>300원대 돌파 및 상승 기대감 존재. 회사 문제 없음에도 불구하고 주가 하락 우려. 마이크로LED, AI 데이터센터 관련 언급.</t>
+          <t>300원대 돌파 기대감 및 마이크로LED, AI 데이터센터 관련 신규 사업 가능성 언급. 로켓 발사 비유로 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4670</v>
+        <v>4725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.61%</t>
+          <t>'+23.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="F3" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G3" t="n">
-        <v>844</v>
+        <v>905</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -693,7 +693,7 @@
         <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>4670</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
         <v>3990</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>173650549873</v>
+        <v>196814350027</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1661</v>
+        <v>1677</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.90%</t>
+          <t>'+20.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>40208797445</v>
+        <v>40751087710</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21550</v>
+        <v>21450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.11%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>243513941620</v>
+        <v>248197873170</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3870</v>
+        <v>3835</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.57%</t>
+          <t>'+9.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>73909897005</v>
+        <v>76039652266</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 기대감 있으나, 주가 하락 및 매집봉 형성 가능성 언급. 부정적 전망 제시.</t>
+          <t>스페이스X 관련 언급이 있으나, 종목 자체의 펀더멘털에 대한 분석 부족. 매집봉 느낌 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우주섹터', '매집봉']</t>
+          <t>['스페이스X']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21600</v>
+        <v>21550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.93%</t>
+          <t>'+6.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>47959385250</v>
+        <v>49197641425</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상에도 불구하고 긍정적 투자 의견 유지. 단기 스퀴즈 및 자사주 소각 가능성 언급.</t>
+          <t>나스닥 반등 및 한투 집중 매수 언급. 60일선 돌파 및 추세 전환 기대감 표출. 투자의견 '매수', 목표주가 4만원 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['나스닥', '금리인상']</t>
+          <t>['추세 전환', '목표주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10470</v>
+        <v>10460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.02%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
         <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>164295493130</v>
+        <v>165662315520</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감 존재. 그러나 매도 물량 출회 및 개인 투자자 손실 발생 가능성 언급.</t>
+          <t>낙태약 및 탈모 치료제 관련 수혜주 언급. 개인 투자자 20만주 손절, 2만원 약진 전망 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13490</v>
+        <v>13350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>46089312255</v>
+        <v>47224064655</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85900</v>
+        <v>85700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G10" t="n">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>78596810050</v>
+        <v>80071205300</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18660</v>
+        <v>18590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H11" t="n">
         <v>10.85</v>
@@ -1438,7 +1438,7 @@
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>35922481645</v>
+        <v>38006224685</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253000</v>
+        <v>252750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G12" t="n">
-        <v>2090</v>
+        <v>1955</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1165363148500</v>
+        <v>1196370737250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>게시글 대부분이 정치 관련 내용으로, 주가 분석과 관련 없는 내용이 주를 이룸.</t>
+          <t>정치 관련 논쟁이 주를 이루며, 삼성전자 자체에 대한 투자 관련 내용은 부실함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16000</v>
+        <v>8410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'-0.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.93</v>
+        <v>-0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>960</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
-        <v>4.88</v>
+        <v>26.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16100</v>
+        <v>8470</v>
       </c>
       <c r="K13" t="n">
-        <v>16200</v>
+        <v>8470</v>
       </c>
       <c r="L13" t="n">
-        <v>16750</v>
+        <v>8510</v>
       </c>
       <c r="M13" t="n">
-        <v>15560</v>
+        <v>8360</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>26.66</v>
       </c>
       <c r="O13" t="n">
-        <v>290610491960</v>
+        <v>8668530500</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-508000</v>
+        <v>-263000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대. 통신 장비 부족 이슈. 2만 원 목표 주가 및 매물대 소화 언급.</t>
+          <t>중국 디스플레이 산업 경쟁 심화 및 회사의 높은 부채 언급. 경영진 무능 비판 및 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '통신 장비']</t>
+          <t>['부채', '영업이익']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8410</v>
+        <v>1742000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>472</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>1467</v>
       </c>
       <c r="H14" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K14" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L14" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M14" t="n">
-        <v>8360</v>
+        <v>1735000</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>8513434520</v>
+        <v>2158150671500</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-263000</v>
+        <v>-161000</v>
       </c>
       <c r="S14" t="n">
-        <v>4000</v>
+        <v>-55000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중국 디스플레이 업체와의 경쟁 심화. 부채 부담 및 경영 능력 비판. 주가 하락 지속 및 반등 가능성 희박.</t>
+          <t>대만 주가 급등 및 ADR 괴리율 언급. 악재 소멸 후 상승 기대감 표출. 외국인 및 기관 매도에 대한 언급도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['디스플레이', '경쟁력']</t>
+          <t>['ADR', '괴리율']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1744000</v>
+        <v>15910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E15" t="n">
+        <v>206</v>
+      </c>
+      <c r="F15" t="n">
+        <v>114</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1083</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>16100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>16200</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16750</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15560</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O15" t="n">
+        <v>300968457595</v>
+      </c>
+      <c r="P15" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-508000</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>465</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1470</v>
-      </c>
-      <c r="H15" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1770000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1785000</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1735000</v>
-      </c>
-      <c r="N15" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2078334636500</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2987000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>333000</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-161000</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-55000</v>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대만 증시 상승 및 악재 소멸 후 상승 기대감 형성. 개인 투자자의 매도 유도 언급.</t>
+          <t>미국 광통신 주가 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망. 통신장비 부족 현상 호재 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대만', '악재소멸']</t>
+          <t>['광통신', '통신장비']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13780</v>
+        <v>3470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K16" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L16" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M16" t="n">
-        <v>13410</v>
+        <v>3445</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>12150810760</v>
+        <v>4966392484</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>132000</v>
+        <v>-279000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 상승 및 겨울 도래로 인한 긍정적 전망과 하락 가능성 공존. 유가 조정 시 등락 반복 패턴 언급.</t>
+          <t>주가 급락 및 폭락에 대한 우려 제기. 상승 가능성 희박하며 상장 폐지 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '겨울']</t>
+          <t>['급락', '상장폐지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3470</v>
+        <v>13750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M17" t="n">
-        <v>3445</v>
+        <v>13410</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4920005731</v>
+        <v>12337443825</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-279000</v>
+        <v>132000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 급락 및 폭락에 대한 우려 제기. 상승 가능성 희박하며 상장 폐지 가능성 언급.</t>
+          <t>유가 변동에 따른 주가 등락 예측. 외국인 매수 언급 있으나, 유가 하락 및 변동성으로 인한 하락세 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급락', '상장폐지']</t>
+          <t>['유가', '변동성']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13120</v>
+        <v>10120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.36</v>
+        <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>18.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13530</v>
+        <v>10460</v>
       </c>
       <c r="K18" t="n">
-        <v>14280</v>
+        <v>10860</v>
       </c>
       <c r="L18" t="n">
-        <v>14800</v>
+        <v>11150</v>
       </c>
       <c r="M18" t="n">
-        <v>13110</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>76147477060</v>
+        <v>52814840775</v>
       </c>
       <c r="P18" t="n">
-        <v>25700</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>4600</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>-64000</v>
+        <v>-60000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10080</v>
+        <v>13030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.8</v>
+        <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="H19" t="n">
-        <v>18.42</v>
+        <v>1.76</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10460</v>
+        <v>13530</v>
       </c>
       <c r="K19" t="n">
-        <v>10860</v>
+        <v>14280</v>
       </c>
       <c r="L19" t="n">
-        <v>11150</v>
+        <v>14800</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>13000</v>
       </c>
       <c r="N19" t="n">
-        <v>19.22</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>52118859105</v>
+        <v>77375964320</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>25700</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>4600</v>
       </c>
       <c r="R19" t="n">
-        <v>-60000</v>
+        <v>-64000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4100</v>
+        <v>4030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.03%</t>
+          <t>'-8.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2260,13 +2260,13 @@
         <v>4420</v>
       </c>
       <c r="M20" t="n">
-        <v>4100</v>
+        <v>4025</v>
       </c>
       <c r="N20" t="n">
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>37620293434</v>
+        <v>40388645589</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_11.xlsx
+++ b/data/trending_integrated_20260917_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>300원대 돌파 기대감 및 마이크로LED, AI 데이터센터 관련 신규 사업 가능성 언급. 로켓 발사 비유로 상승 기대.</t>
+          <t>마이크로LED, AI 데이터센터 관련 테마 언급 및 300원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['마이크로LED', 'AI데이터센터']</t>
+          <t>['마이크로LED', 'AI', '데이터센터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4725</v>
+        <v>4675</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.05%</t>
+          <t>'+21.74%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="F3" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>905</v>
+        <v>951</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>196814350027</v>
+        <v>206313292435</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오 및 소프트뱅크 인수 가능성에 대한 높은 기대감 형성. 텐버거 및 10배 상승 전망. 거래량 폭발 예상.</t>
+          <t>카카오 또는 소프트뱅크 인수설 기반 10배 상승 기대감. 거래량 급증 및 손바뀜 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['카카오', '소프트뱅크', '인수']</t>
+          <t>['인수설', '소프트뱅크', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1677</v>
+        <v>1683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.04%</t>
+          <t>'+20.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>40751087710</v>
+        <v>41227903344</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21450</v>
+        <v>21400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.57%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>248197873170</v>
+        <v>251740435595</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3835</v>
+        <v>3825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.57%</t>
+          <t>'+9.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" t="n">
         <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>76039652266</v>
+        <v>77087523517</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 언급이 있으나, 종목 자체의 펀더멘털에 대한 분석 부족. 매집봉 느낌 언급.</t>
+          <t>스페이스X 관련 테마 상승 기대감 및 프로그램 매수세 유입 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X']</t>
+          <t>['스페이스X', '테마', '프로그램매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21550</v>
+        <v>21500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.68%</t>
+          <t>'+6.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>49197641425</v>
+        <v>51033427625</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10460</v>
+        <v>10530</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.91%</t>
+          <t>'+5.62%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>165662315520</v>
+        <v>166781990040</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 수혜주 언급. 개인 투자자 20만주 손절, 2만원 약진 전망 제기.</t>
+          <t>낙태약 도입 및 탈모치료 관련 수혜 기대감 형성. 예상 매출 1조원 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료']</t>
+          <t>['낙태약', '탈모치료', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13350</v>
+        <v>13390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+3.64%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>47224064655</v>
+        <v>48142195765</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>80071205300</v>
+        <v>81666111850</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18590</v>
+        <v>18580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
         <v>44</v>
@@ -1432,13 +1432,13 @@
         <v>18900</v>
       </c>
       <c r="M11" t="n">
-        <v>18580</v>
+        <v>18510</v>
       </c>
       <c r="N11" t="n">
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>38006224685</v>
+        <v>39709405475</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252750</v>
+        <v>253500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>439</v>
       </c>
       <c r="G12" t="n">
-        <v>1955</v>
+        <v>1854</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1196370737250</v>
+        <v>1223933066750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치 관련 논쟁이 주를 이루며, 삼성전자 자체에 대한 투자 관련 내용은 부실함.</t>
+          <t>정치적 언급이 주를 이루며, 종목 자체에 대한 분석이나 정보는 부재함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1590,13 +1590,13 @@
         <v>-0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F13" t="n">
         <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H13" t="n">
         <v>26.54</v>
@@ -1622,7 +1622,7 @@
         <v>26.66</v>
       </c>
       <c r="O13" t="n">
-        <v>8668530500</v>
+        <v>8775498590</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업 경쟁 심화 및 회사의 높은 부채 언급. 경영진 무능 비판 및 주가 하락 전망.</t>
+          <t>중국과의 경쟁 열위, 높은 부채 및 무능한 경영진에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['부채', '영업이익']</t>
+          <t>['중국', '부채', '경영진']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1742000</v>
+        <v>1746000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>472</v>
       </c>
       <c r="G14" t="n">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2158150671500</v>
+        <v>2219809038500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대만 주가 급등 및 ADR 괴리율 언급. 악재 소멸 후 상승 기대감 표출. 외국인 및 기관 매도에 대한 언급도 존재.</t>
+          <t>대만 증시 상승 및 ADR 괴리율 언급과 함께 상승 기대감 표현.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ADR', '괴리율']</t>
+          <t>['ADR', '괴리율', '상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15910</v>
+        <v>15930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2.93</v>
       </c>
       <c r="E15" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
         <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>1083</v>
+        <v>1134</v>
       </c>
       <c r="H15" t="n">
         <v>4.88</v>
@@ -1806,7 +1806,7 @@
         <v>1.95</v>
       </c>
       <c r="O15" t="n">
-        <v>300968457595</v>
+        <v>304233462315</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망. 통신장비 부족 현상 호재 언급.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비']</t>
+          <t>['광통신', '미국', '수혜']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3470</v>
+        <v>3460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H16" t="n">
         <v>2.26</v>
@@ -1898,7 +1898,7 @@
         <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>4966392484</v>
+        <v>5024052969</v>
       </c>
       <c r="P16" t="n">
         <v>16110</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 급락 및 폭락에 대한 우려 제기. 상승 가능성 희박하며 상장 폐지 가능성 언급.</t>
+          <t>급락세 지속 및 상장폐지 가능성 언급. 차익 실현 후 하락 전환 예상.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['급락', '상장폐지']</t>
+          <t>['급락', '상장폐지', '차익실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13750</v>
+        <v>13730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H17" t="n">
         <v>0.01</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>12337443825</v>
+        <v>12670761665</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동에 따른 주가 등락 예측. 외국인 매수 언급 있으나, 유가 하락 및 변동성으로 인한 하락세 전망.</t>
+          <t>유가 변동성에 따른 등락 반복 및 단기 차익 거래 패턴 관찰.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '변동성']</t>
+          <t>['유가', '변동성', '차익거래']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10120</v>
+        <v>10200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H18" t="n">
         <v>18.42</v>
@@ -2082,7 +2082,7 @@
         <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>52814840775</v>
+        <v>53234999755</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.77%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="n">
         <v>1.76</v>
@@ -2168,13 +2168,13 @@
         <v>14800</v>
       </c>
       <c r="M19" t="n">
-        <v>13000</v>
+        <v>12960</v>
       </c>
       <c r="N19" t="n">
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>77375964320</v>
+        <v>78002206890</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4030</v>
+        <v>4065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.62%</t>
+          <t>'-7.82%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>40388645589</v>
+        <v>42072484217</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_11.xlsx
+++ b/data/trending_integrated_20260917_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>마이크로LED, AI 데이터센터 관련 테마 언급 및 300원 돌파 기대감.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 96건 토론 포착</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['마이크로LED', 'AI', '데이터센터']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4675</v>
+        <v>4640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.74%</t>
+          <t>'+20.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
-        <v>951</v>
+        <v>1012</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>206313292435</v>
+        <v>211328149687</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오 또는 소프트뱅크 인수설 기반 10배 상승 기대감. 거래량 급증 및 손바뀜 관찰.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 404건 토론 포착</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수설', '소프트뱅크', '거래량']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1683</v>
+        <v>1667</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.47%</t>
+          <t>'+19.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>41227903344</v>
+        <v>41500983929</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -854,13 +854,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
         <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>251740435595</v>
+        <v>253827903270</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3825</v>
+        <v>3875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.29%</t>
+          <t>'+10.71%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>77087523517</v>
+        <v>78535786697</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 테마 상승 기대감 및 프로그램 매수세 유입 관찰.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 107건 토론 포착</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '테마', '프로그램매수']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>51033427625</v>
+        <v>53436439825</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 한투 집중 매수 언급. 60일선 돌파 및 추세 전환 기대감 표출. 투자의견 '매수', 목표주가 4만원 제시.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 86건 토론 포착</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['추세 전환', '목표주가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10530</v>
+        <v>10435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.62%</t>
+          <t>'+4.66%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>166781990040</v>
+        <v>167873927705</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1222,13 +1222,13 @@
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>48142195765</v>
+        <v>48543552560</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85700</v>
+        <v>85800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>81666111850</v>
+        <v>82811582200</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18580</v>
+        <v>18645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.05%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="H11" t="n">
         <v>10.85</v>
@@ -1438,7 +1438,7 @@
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>39709405475</v>
+        <v>40239655765</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253500</v>
+        <v>16090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>216</v>
       </c>
       <c r="F12" t="n">
-        <v>439</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>1854</v>
+        <v>1164</v>
       </c>
       <c r="H12" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>253500</v>
+        <v>16100</v>
       </c>
       <c r="K12" t="n">
-        <v>257000</v>
+        <v>16200</v>
       </c>
       <c r="L12" t="n">
-        <v>259000</v>
+        <v>16750</v>
       </c>
       <c r="M12" t="n">
-        <v>252000</v>
+        <v>15560</v>
       </c>
       <c r="N12" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1223933066750</v>
+        <v>307428823145</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>77100</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-199000</v>
+        <v>-508000</v>
       </c>
       <c r="S12" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 언급이 주를 이루며, 종목 자체에 대한 분석이나 정보는 부재함.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['광통신', '미국', '수혜']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8410</v>
+        <v>253250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'-0.10%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>435</v>
       </c>
       <c r="G13" t="n">
-        <v>229</v>
+        <v>1830</v>
       </c>
       <c r="H13" t="n">
-        <v>26.54</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8470</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>8470</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>8510</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>8360</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>26.66</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>8775498590</v>
+        <v>1260421572750</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-263000</v>
+        <v>-199000</v>
       </c>
       <c r="S13" t="n">
-        <v>4000</v>
+        <v>-55000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>중국과의 경쟁 열위, 높은 부채 및 무능한 경영진에 대한 부정적 전망.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['중국', '부채', '경영진']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1746000</v>
+        <v>1747000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>1479</v>
+        <v>1511</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2219809038500</v>
+        <v>2275646140500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대만 증시 상승 및 ADR 괴리율 언급과 함께 상승 기대감 표현.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ADR', '괴리율', '상승']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15930</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.06%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.93</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>1134</v>
+        <v>238</v>
       </c>
       <c r="H15" t="n">
-        <v>4.88</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16100</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>16200</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>16750</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>15560</v>
+        <v>8360</v>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>304233462315</v>
+        <v>8994949270</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-508000</v>
+        <v>-263000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 107건 토론 포착</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '수혜']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3460</v>
+        <v>13740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K16" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M16" t="n">
-        <v>3445</v>
+        <v>13410</v>
       </c>
       <c r="N16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5024052969</v>
+        <v>12937950575</v>
       </c>
       <c r="P16" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-279000</v>
+        <v>132000</v>
       </c>
       <c r="S16" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>급락세 지속 및 상장폐지 가능성 언급. 차익 실현 후 하락 전환 예상.</t>
+          <t>유가 변동성에 따른 등락 반복 및 단기 차익 거래 패턴 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['급락', '상장폐지', '차익실현']</t>
+          <t>['유가', '변동성', '차익거래']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13730</v>
+        <v>3440</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-2.27%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>13410</v>
+        <v>3440</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>12670761665</v>
+        <v>5079997168</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>132000</v>
+        <v>-279000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 등락 반복 및 단기 차익 거래 패턴 관찰.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 86건 토론 포착</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '변동성', '차익거래']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10200</v>
+        <v>10190</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H18" t="n">
         <v>18.42</v>
@@ -2082,7 +2082,7 @@
         <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>53234999755</v>
+        <v>53782063845</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13020</v>
+        <v>13120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
         <v>1.76</v>
@@ -2174,7 +2174,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>78002206890</v>
+        <v>78358105620</v>
       </c>
       <c r="P19" t="n">
         <v>25700</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4065</v>
+        <v>4100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-7.03%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>42072484217</v>
+        <v>42821632810</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
